--- a/POTAL_Feature_Health_Check.xlsx
+++ b/POTAL_Feature_Health_Check.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="No API Endpoint" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Failed Features" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI Manual Check" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No API Endpoint" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failed Features" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +51,50 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00CC6600"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -94,8 +137,28 @@
         <bgColor rgb="00DC2626"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,11 +180,17 @@
         <color rgb="00E5E7EB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,6 +216,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -572,7 +657,6 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -636,7 +720,6 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1025,6 +1108,112 @@
       <c r="G33" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>UI Manual Check (Cowork Chrome MCP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Check Date</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:42 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Total Checked</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>61/65 (93.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>Issues Found:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>FAIL: F120 Cookie Consent - No cookie banner on any page (GDPR/CCPA required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>WARN: F118 Terms of Service - Still shows old paid plans (Basic/Pro/Enterprise). Needs Forever Free update</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>WARN: F123 Security Headers - CSP and HSTS headers missing (5/7 set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>WARN: F035 Multi-language UI - EN button exists but language dropdown not functional</t>
         </is>
       </c>
     </row>
@@ -1034,6 +1223,2471 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Feature ID</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Feature Name</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>Check Method</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>Page/URL</t>
+        </is>
+      </c>
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="26" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>F104</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Landing Page</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="27" t="inlineStr">
+        <is>
+          <t>Hero, CTA, stats, widget preview all working</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>F105</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>Pricing Page</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D3" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>/pricing</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>Forever Free plan, Enterprise Contact Us</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>F106</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Blog</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>/blog</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Articles listing with categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>F107</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>SEO Optimization</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>JS Check</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>meta desc, og:title, canonical, robots all set</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>F127</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>/help</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>FAQ accordion, search, 5 categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>F131</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Community Forum</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>/community</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>9 categories, voting, search, filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>F041</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>/dashboard</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t>Redirects to /auth/login (auth required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>F088</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>User Management</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>/auth/login</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="inlineStr">
+        <is>
+          <t>Email/password + Google SSO login</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>F089</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Role-based Access</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>/auth/signup</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="inlineStr">
+        <is>
+          <t>Signup with Company Name + Country</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>F113</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>SSO Support</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>/auth/login</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t>Continue with Google button present</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>F140</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Onboarding Wizard</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>/features/onboarding-wizard</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>F141</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Product Tour</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>/features/product-tour</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>F035</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Multi-language UI</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="inlineStr">
+        <is>
+          <t>EN button exists but dropdown not opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>F036</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>REST API</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>/developers</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>API Reference section with endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>F037</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>API Key Auth</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>/developers</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>Authentication section present</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>F038</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Rate Limiting</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>/features/rate-limiting</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>F091</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>API Documentation</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>/developers/docs</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>Full API docs page (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>F092</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Sandbox Environment</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>/features/sandbox-environment</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>F097</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>/nonexistent</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>Custom 404 with Go Home/Try API/Widget/Help</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>F098</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Versioned API</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>/developers</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>/api/v1/ prefix on all endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Uptime Monitoring</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>/features/uptime-monitoring</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>F102</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Incident Response</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>/features/incident-response</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>F112</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Multi-tenant</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>/features/multi-tenant</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>F115</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Data Retention</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>/features/data-retention</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>F128</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>API Changelog</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>/features/api-changelog</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>F129</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Migration Guide</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>/features/migration-guide</t>
+        </is>
+      </c>
+      <c r="F27" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>F080</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Custom Reports</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>/features/custom-reports</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>F081</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Data Visualization</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="inlineStr">
+        <is>
+          <t>Competitor comparison chart on homepage</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>F086</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Email Notifications</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>/features/email-notifications</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>F045</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Shopify App</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>/features/shopify-app</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>F046</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>WooCommerce Plugin</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>/features/woocommerce-plugin</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>F047</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>BigCommerce Plugin</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>/features/bigcommerce-plugin</t>
+        </is>
+      </c>
+      <c r="F33" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>F048</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Magento Module</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>/features/magento-module</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>F049</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>JS Widget</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F35" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="inlineStr">
+        <is>
+          <t>Widget preview on homepage + playground</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>F050</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>SDK (JavaScript)</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>/features/sdk-javascript</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>F051</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>SDK (Python)</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>/features/sdk-python</t>
+        </is>
+      </c>
+      <c r="F37" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>F052</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>SDK (cURL)</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>/developers</t>
+        </is>
+      </c>
+      <c r="F38" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>cURL example in Try It Live section</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>F061</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Carrier Integration</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>/features/carrier-integration</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>F063</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>/features/tracking</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>F065</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>Dimensional Weight</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>/features/dimensional-weight</t>
+        </is>
+      </c>
+      <c r="F41" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>F066</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>Insurance Calc</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>/features/insurance-calc</t>
+        </is>
+      </c>
+      <c r="F42" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>F068</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>Multi-package</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>/features/multi-package</t>
+        </is>
+      </c>
+      <c r="F43" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>F069</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>3PL Integration</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>/features/3pl-integration</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>F070</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>Multi-warehouse</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>/features/multi-warehouse</t>
+        </is>
+      </c>
+      <c r="F45" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="27" t="inlineStr">
+        <is>
+          <t>F121</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Data Encryption</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D46" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>/features/data-encryption</t>
+        </is>
+      </c>
+      <c r="F46" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>F122</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>/features/access-control</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>F123</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>Security Headers</t>
+        </is>
+      </c>
+      <c r="C48" s="27" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>JS Check</t>
+        </is>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G48" s="27" t="inlineStr">
+        <is>
+          <t>5/7 headers set. CSP &amp; HSTS missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>F124</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Vulnerability Scanning</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>/features/vulnerability-scanning</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>F125</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>Penetration Testing</t>
+        </is>
+      </c>
+      <c r="C50" s="27" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>/features/penetration-testing</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>F116</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>GDPR Compliance</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>/features/gdpr-compliance</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200). Footer: GDPR COMPLIANT badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>F117</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>CCPA Compliance</t>
+        </is>
+      </c>
+      <c r="C52" s="27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>/features/ccpa-compliance</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>F118</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>Terms of Service</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>/terms</t>
+        </is>
+      </c>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="G53" s="27" t="inlineStr">
+        <is>
+          <t>Page exists but shows old paid plans (Basic/Pro/Enterprise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>F119</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>Privacy Policy</t>
+        </is>
+      </c>
+      <c r="C54" s="27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>Chrome MCP</t>
+        </is>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>/privacy</t>
+        </is>
+      </c>
+      <c r="F54" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="27" t="inlineStr">
+        <is>
+          <t>Full privacy policy, March 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>F120</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>Cookie Consent</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="inlineStr">
+        <is>
+          <t>JS Check</t>
+        </is>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G55" s="27" t="inlineStr">
+        <is>
+          <t>No cookie consent banner found on any page</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>F111</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>Compliance Certificates</t>
+        </is>
+      </c>
+      <c r="C56" s="27" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+      <c r="D56" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>/features/compliance-certificates</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>F130</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>Video Tutorials</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>/features/video-tutorials</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>F133</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>Referral Program</t>
+        </is>
+      </c>
+      <c r="C58" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D58" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>/features/referral-program</t>
+        </is>
+      </c>
+      <c r="F58" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>F134</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>Affiliate System</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>/features/affiliate-system</t>
+        </is>
+      </c>
+      <c r="F59" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>F135</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>Reseller Program</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D60" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>/features/reseller-program</t>
+        </is>
+      </c>
+      <c r="F60" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>F136</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Training Program</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D61" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>/features/training-program</t>
+        </is>
+      </c>
+      <c r="F61" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>F137</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C62" s="27" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D62" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>/features/certification</t>
+        </is>
+      </c>
+      <c r="F62" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>F142</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>Email Campaigns</t>
+        </is>
+      </c>
+      <c r="C63" s="27" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>/features/email-campaigns</t>
+        </is>
+      </c>
+      <c r="F63" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>F144</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>Sentiment Analysis</t>
+        </is>
+      </c>
+      <c r="C64" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>/features/sentiment-analysis</t>
+        </is>
+      </c>
+      <c r="F64" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>F145</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>A/B Testing</t>
+        </is>
+      </c>
+      <c r="C65" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D65" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>/features/a-b-testing</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G65" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (slug: a-b-testing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>F146</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>Feature Flags</t>
+        </is>
+      </c>
+      <c r="C66" s="27" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D66" s="27" t="inlineStr">
+        <is>
+          <t>URL Check</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>/features/feature-flags</t>
+        </is>
+      </c>
+      <c r="F66" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" s="27" t="inlineStr">
+        <is>
+          <t>Feature page exists (200)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7496,7 +10150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9299,7 +11953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
